--- a/sheets/대금율보/검수/부초같은 인생.xlsx
+++ b/sheets/대금율보/검수/부초같은 인생.xlsx
@@ -5361,7 +5361,7 @@
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㳞
-淋㳞‹</t>
+淋㳞</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -5397,7 +5397,7 @@
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–㳞
-淋㳞‹</t>
+淋㳞</t>
         </is>
       </c>
       <c r="O4" s="23"/>
@@ -5429,7 +5429,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△淋‹
+          <t xml:space="preserve">△淋
 –㳞</t>
         </is>
       </c>
@@ -5751,7 +5751,7 @@
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="O10" s="26"/>
@@ -5767,7 +5767,7 @@
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 –潕</t>
         </is>
       </c>
@@ -5825,11 +5825,7 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
@@ -5986,7 +5982,7 @@
       <c r="M14" s="26"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O14" s="26"/>
@@ -6019,7 +6015,7 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞‹
+          <t xml:space="preserve">汰㳞
 –㳞</t>
         </is>
       </c>
@@ -6121,7 +6117,7 @@
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C17" s="23"/>
@@ -6225,7 +6221,7 @@
       </c>
       <c r="N18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
@@ -6235,7 +6231,7 @@
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
@@ -6254,7 +6250,7 @@
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢‹
+          <t xml:space="preserve">潢潢
 –無</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/부초같은 인생.xlsx
+++ b/sheets/대금율보/검수/부초같은 인생.xlsx
@@ -5266,26 +5266,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="76.92" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="O6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="O10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.77" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.77" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.77" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.77" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="O14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.77" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.77" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.77" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.77" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="O18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="68.77" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="O19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="68.77" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="O20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="68.77" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="O21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="68.77" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -6452,6 +6452,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
 </worksheet>
 </file>